--- a/tools/config/affix.xlsx
+++ b/tools/config/affix.xlsx
@@ -1,20 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="affix" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-07-01T04:42:01Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-07-01T04:42:16Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -124,7 +124,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -407,7 +407,22 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="affix" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -429,20 +444,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>numeric_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>modifier_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>min_per_level</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>max_per_level</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>slot_mask</t>
         </is>
@@ -466,22 +486,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>comma</t>
         </is>
@@ -501,20 +526,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>NumericType 枚举值</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>ModifierType 枚举值 1=固定 2=百分比</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>每级最小系数</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>每级最大系数</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>可出现的装备槽 slot_type 列表</t>
         </is>
@@ -536,10 +566,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,7 +677,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
